--- a/fractionation.xlsx
+++ b/fractionation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/f005cbk/Documents/lab/NC10_Radboud/code/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{594407B1-A5CC-3A44-9472-21DF6438616B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{47BB5777-90C3-C544-8F8A-5155F0A2DB4F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16440" xr2:uid="{2C52F002-3CBE-A64B-89A4-09B4655299CB}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="255" uniqueCount="125">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="275" uniqueCount="125">
   <si>
     <t>Sample</t>
   </si>
@@ -377,9 +377,6 @@
     <t>Li et al., 2024 (pMMO, 21C)</t>
   </si>
   <si>
-    <t>Wegner et al., 2021</t>
-  </si>
-  <si>
     <t>Previous studies, sulfate-AOM, mcr</t>
   </si>
   <si>
@@ -408,6 +405,9 @@
   </si>
   <si>
     <t>Wang et al., 2016 (pMMO, 30C)</t>
+  </si>
+  <si>
+    <t>R17 (first 3 points)</t>
   </si>
 </sst>
 </file>
@@ -918,7 +918,7 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
     <xf numFmtId="0" fontId="0" fillId="33" borderId="0" xfId="0" applyFill="1"/>
@@ -926,6 +926,7 @@
     <xf numFmtId="172" fontId="19" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="172" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="172" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -2516,6 +2517,769 @@
 </c:chartSpace>
 </file>
 
+<file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US" altLang="zh-CN"/>
+              <a:t>R17</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="zh-CN" altLang="en-US"/>
+              <a:t> </a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="en-US" altLang="zh-CN"/>
+              <a:t>fractionation</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="zh-CN" altLang="en-US" baseline="0"/>
+              <a:t> </a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="en-US" altLang="zh-CN" baseline="0"/>
+              <a:t>factors</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="zh-CN" altLang="en-US" baseline="0"/>
+              <a:t> </a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="en-US" altLang="zh-CN" baseline="0"/>
+              <a:t>(First</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="zh-CN" altLang="en-US" baseline="0"/>
+              <a:t> </a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="en-US" altLang="zh-CN" baseline="0"/>
+              <a:t>3</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="zh-CN" altLang="en-US" baseline="0"/>
+              <a:t> </a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="en-US" altLang="zh-CN" baseline="0"/>
+              <a:t>points)</a:t>
+            </a:r>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:scatterChart>
+        <c:scatterStyle val="lineMarker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:spPr>
+            <a:ln w="25400" cap="rnd">
+              <a:noFill/>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:trendline>
+            <c:spPr>
+              <a:ln w="19050" cap="rnd">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+                <a:prstDash val="sysDot"/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:trendlineType val="linear"/>
+            <c:dispRSqr val="1"/>
+            <c:dispEq val="1"/>
+            <c:trendlineLbl>
+              <c:layout>
+                <c:manualLayout>
+                  <c:x val="-6.8003616772783784E-2"/>
+                  <c:y val="-0.10270122484689413"/>
+                </c:manualLayout>
+              </c:layout>
+              <c:numFmt formatCode="General" sourceLinked="0"/>
+              <c:spPr>
+                <a:noFill/>
+                <a:ln>
+                  <a:noFill/>
+                </a:ln>
+                <a:effectLst/>
+              </c:spPr>
+              <c:txPr>
+                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+                <a:lstStyle/>
+                <a:p>
+                  <a:pPr>
+                    <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="65000"/>
+                          <a:lumOff val="35000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:latin typeface="+mn-lt"/>
+                      <a:ea typeface="+mn-ea"/>
+                      <a:cs typeface="+mn-cs"/>
+                    </a:defRPr>
+                  </a:pPr>
+                  <a:endParaRPr lang="en-US"/>
+                </a:p>
+              </c:txPr>
+            </c:trendlineLbl>
+          </c:trendline>
+          <c:xVal>
+            <c:numRef>
+              <c:f>isotope_data!$R$16:$R$18</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="3"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.30611396627248577</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.32103782000218861</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>isotope_data!$X$16:$X$18</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="3"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>4.8934100930869882E-2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>7.7672004552973947E-2</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-363D-B94F-841D-E511CBB27D85}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:spPr>
+            <a:ln w="25400" cap="rnd">
+              <a:noFill/>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent2"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:trendline>
+            <c:spPr>
+              <a:ln w="19050" cap="rnd">
+                <a:solidFill>
+                  <a:schemeClr val="accent2"/>
+                </a:solidFill>
+                <a:prstDash val="sysDot"/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:trendlineType val="linear"/>
+            <c:dispRSqr val="1"/>
+            <c:dispEq val="1"/>
+            <c:trendlineLbl>
+              <c:layout>
+                <c:manualLayout>
+                  <c:x val="1.6356478167501701E-2"/>
+                  <c:y val="-7.8858267716535438E-2"/>
+                </c:manualLayout>
+              </c:layout>
+              <c:numFmt formatCode="General" sourceLinked="0"/>
+              <c:spPr>
+                <a:noFill/>
+                <a:ln>
+                  <a:noFill/>
+                </a:ln>
+                <a:effectLst/>
+              </c:spPr>
+              <c:txPr>
+                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+                <a:lstStyle/>
+                <a:p>
+                  <a:pPr>
+                    <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="65000"/>
+                          <a:lumOff val="35000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:latin typeface="+mn-lt"/>
+                      <a:ea typeface="+mn-ea"/>
+                      <a:cs typeface="+mn-cs"/>
+                    </a:defRPr>
+                  </a:pPr>
+                  <a:endParaRPr lang="en-US"/>
+                </a:p>
+              </c:txPr>
+            </c:trendlineLbl>
+          </c:trendline>
+          <c:xVal>
+            <c:numRef>
+              <c:f>isotope_data!$R$16:$R$18</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="3"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.30611396627248577</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.32103782000218861</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>isotope_data!$T$16:$T$18</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="3"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>5.7159534194998075E-3</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>8.9763155062316524E-3</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000008-363D-B94F-841D-E511CBB27D85}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:spPr>
+            <a:ln w="25400" cap="rnd">
+              <a:noFill/>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent3"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent3"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:trendline>
+            <c:spPr>
+              <a:ln w="19050" cap="rnd">
+                <a:solidFill>
+                  <a:schemeClr val="accent3"/>
+                </a:solidFill>
+                <a:prstDash val="sysDot"/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:trendlineType val="linear"/>
+            <c:dispRSqr val="0"/>
+            <c:dispEq val="1"/>
+            <c:trendlineLbl>
+              <c:numFmt formatCode="General" sourceLinked="0"/>
+              <c:spPr>
+                <a:noFill/>
+                <a:ln>
+                  <a:noFill/>
+                </a:ln>
+                <a:effectLst/>
+              </c:spPr>
+              <c:txPr>
+                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+                <a:lstStyle/>
+                <a:p>
+                  <a:pPr>
+                    <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="65000"/>
+                          <a:lumOff val="35000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:latin typeface="+mn-lt"/>
+                      <a:ea typeface="+mn-ea"/>
+                      <a:cs typeface="+mn-cs"/>
+                    </a:defRPr>
+                  </a:pPr>
+                  <a:endParaRPr lang="en-US"/>
+                </a:p>
+              </c:txPr>
+            </c:trendlineLbl>
+          </c:trendline>
+          <c:xVal>
+            <c:numRef>
+              <c:f>isotope_data!$R$16:$R$18</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="3"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.30611396627248577</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.32103782000218861</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>isotope_data!$V$16:$V$18</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="3"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>4.34272172386614E-2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>6.9271628984375139E-2</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{0000000A-363D-B94F-841D-E511CBB27D85}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="3"/>
+          <c:order val="3"/>
+          <c:spPr>
+            <a:ln w="25400" cap="rnd">
+              <a:noFill/>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent4"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent4"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:trendline>
+            <c:spPr>
+              <a:ln w="19050" cap="rnd">
+                <a:solidFill>
+                  <a:schemeClr val="accent4"/>
+                </a:solidFill>
+                <a:prstDash val="sysDot"/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:trendlineType val="linear"/>
+            <c:dispRSqr val="0"/>
+            <c:dispEq val="1"/>
+            <c:trendlineLbl>
+              <c:numFmt formatCode="General" sourceLinked="0"/>
+              <c:spPr>
+                <a:noFill/>
+                <a:ln>
+                  <a:noFill/>
+                </a:ln>
+                <a:effectLst/>
+              </c:spPr>
+              <c:txPr>
+                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+                <a:lstStyle/>
+                <a:p>
+                  <a:pPr>
+                    <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="65000"/>
+                          <a:lumOff val="35000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:latin typeface="+mn-lt"/>
+                      <a:ea typeface="+mn-ea"/>
+                      <a:cs typeface="+mn-cs"/>
+                    </a:defRPr>
+                  </a:pPr>
+                  <a:endParaRPr lang="en-US"/>
+                </a:p>
+              </c:txPr>
+            </c:trendlineLbl>
+          </c:trendline>
+          <c:xVal>
+            <c:numRef>
+              <c:f>isotope_data!$R$16:$R$18</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="3"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.30611396627248577</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.32103782000218861</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>isotope_data!$Z$16:$Z$18</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="3"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>7.8543709094870739E-2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.12719879121153083</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{0000000C-363D-B94F-841D-E511CBB27D85}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="1711475295"/>
+        <c:axId val="1711477023"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="1711475295"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1711477023"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="1711477023"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1711475295"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
 <file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
   <a:schemeClr val="accent1"/>
@@ -2557,6 +3321,46 @@
 </file>
 
 <file path=xl/charts/colors2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors3.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
   <a:schemeClr val="accent1"/>
   <a:schemeClr val="accent2"/>
@@ -3628,20 +4432,536 @@
 </cs:chartStyle>
 </file>
 
+<file path=xl/charts/style3.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>30</xdr:col>
-      <xdr:colOff>349250</xdr:colOff>
+      <xdr:col>31</xdr:col>
+      <xdr:colOff>184150</xdr:colOff>
       <xdr:row>1</xdr:row>
-      <xdr:rowOff>139700</xdr:rowOff>
+      <xdr:rowOff>127000</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>35</xdr:col>
-      <xdr:colOff>793750</xdr:colOff>
+      <xdr:col>36</xdr:col>
+      <xdr:colOff>628650</xdr:colOff>
       <xdr:row>15</xdr:row>
-      <xdr:rowOff>38100</xdr:rowOff>
+      <xdr:rowOff>25400</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -3699,6 +5019,44 @@
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
           <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>26</xdr:col>
+      <xdr:colOff>711200</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>165100</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>31</xdr:col>
+      <xdr:colOff>127000</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>63500</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="5" name="Chart 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{31A47156-CEAA-5645-B1E3-E3A1D5BAAED7}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -5729,6 +7087,35 @@
         <v>0.87254769685751143</v>
       </c>
     </row>
+    <row r="21" spans="1:43">
+      <c r="AD21" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="AE21">
+        <f>1-0.0238</f>
+        <v>0.97619999999999996</v>
+      </c>
+      <c r="AF21">
+        <f>1-0.1823</f>
+        <v>0.81769999999999998</v>
+      </c>
+      <c r="AG21">
+        <f>1-0.2048</f>
+        <v>0.79520000000000002</v>
+      </c>
+      <c r="AH21">
+        <f>1-0.333</f>
+        <v>0.66700000000000004</v>
+      </c>
+      <c r="AI21" s="2">
+        <f>AG21/AE21/AF21</f>
+        <v>0.99619319403114914</v>
+      </c>
+      <c r="AJ21" s="2">
+        <f>AH21/AF21^2</f>
+        <v>0.99755727089209112</v>
+      </c>
+    </row>
     <row r="22" spans="1:43">
       <c r="A22" t="s">
         <v>13</v>
@@ -6044,7 +7431,7 @@
         <v>98</v>
       </c>
       <c r="AQ24" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="25" spans="1:43">
@@ -6851,7 +8238,7 @@
     </row>
     <row r="32" spans="1:43">
       <c r="AD32" s="6" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
     </row>
     <row r="33" spans="1:42">
@@ -6977,6 +8364,42 @@
       <c r="AD34" t="s">
         <v>111</v>
       </c>
+      <c r="AE34">
+        <v>0.99250000000000005</v>
+      </c>
+      <c r="AF34">
+        <v>1E-4</v>
+      </c>
+      <c r="AG34">
+        <v>0.84599999999999997</v>
+      </c>
+      <c r="AH34">
+        <v>1E-3</v>
+      </c>
+      <c r="AI34">
+        <v>0.82699999999999996</v>
+      </c>
+      <c r="AJ34">
+        <v>2E-3</v>
+      </c>
+      <c r="AK34">
+        <v>0.65</v>
+      </c>
+      <c r="AL34">
+        <v>3.0000000000000001E-3</v>
+      </c>
+      <c r="AM34">
+        <v>0.98499999999999999</v>
+      </c>
+      <c r="AN34">
+        <v>2E-3</v>
+      </c>
+      <c r="AO34">
+        <v>0.90900000000000003</v>
+      </c>
+      <c r="AP34">
+        <v>5.0000000000000001E-3</v>
+      </c>
     </row>
     <row r="35" spans="1:42">
       <c r="A35" t="s">
@@ -7019,7 +8442,7 @@
         <v>43</v>
       </c>
       <c r="AD35" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="AE35">
         <f>1-17/1000</f>
@@ -7046,10 +8469,10 @@
         <v>6.4085879880048458E-3</v>
       </c>
       <c r="AK35" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="AL35" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="AM35" s="5">
         <f>AI35/AG35/AE35</f>
@@ -7059,10 +8482,10 @@
         <v>4.0000000000000002E-4</v>
       </c>
       <c r="AO35" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="AP35" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="36" spans="1:42">
@@ -7106,7 +8529,7 @@
         <v>43</v>
       </c>
       <c r="AD36" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="AE36">
         <f>1-0.0183</f>
@@ -7133,10 +8556,10 @@
         <v>8.8684835231284051E-3</v>
       </c>
       <c r="AK36" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="AL36" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="AM36" s="5">
         <f>AI36/AG36/AE36</f>
@@ -7146,10 +8569,10 @@
         <v>1E-3</v>
       </c>
       <c r="AO36" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="AP36" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="37" spans="1:42">
@@ -7192,8 +8615,8 @@
       <c r="Q37" t="s">
         <v>43</v>
       </c>
-      <c r="AD37" t="s">
-        <v>114</v>
+      <c r="AD37" s="6" t="s">
+        <v>104</v>
       </c>
     </row>
     <row r="38" spans="1:42">
@@ -7236,8 +8659,44 @@
       <c r="Q38" t="s">
         <v>43</v>
       </c>
-      <c r="AD38" s="6" t="s">
-        <v>104</v>
+      <c r="AD38" t="s">
+        <v>105</v>
+      </c>
+      <c r="AE38">
+        <v>0.98485</v>
+      </c>
+      <c r="AF38">
+        <v>6.0000000000000002E-5</v>
+      </c>
+      <c r="AG38">
+        <v>0.72650000000000003</v>
+      </c>
+      <c r="AH38">
+        <v>1E-3</v>
+      </c>
+      <c r="AI38">
+        <v>0.71409999999999996</v>
+      </c>
+      <c r="AJ38">
+        <v>1.1000000000000001E-3</v>
+      </c>
+      <c r="AK38">
+        <v>0.47570000000000001</v>
+      </c>
+      <c r="AL38">
+        <v>2.3E-3</v>
+      </c>
+      <c r="AM38">
+        <v>0.99809999999999999</v>
+      </c>
+      <c r="AN38">
+        <v>1.6999999999999999E-3</v>
+      </c>
+      <c r="AO38">
+        <v>0.90129999999999999</v>
+      </c>
+      <c r="AP38">
+        <v>4.4999999999999997E-3</v>
       </c>
     </row>
     <row r="39" spans="1:42">
@@ -7281,43 +8740,45 @@
         <v>43</v>
       </c>
       <c r="AD39" t="s">
-        <v>105</v>
+        <v>122</v>
       </c>
       <c r="AE39">
-        <v>0.98485</v>
+        <v>0.97799999999999998</v>
       </c>
       <c r="AF39">
-        <v>6.0000000000000002E-5</v>
+        <v>1E-3</v>
       </c>
       <c r="AG39">
-        <v>0.72650000000000003</v>
+        <v>0.79800000000000004</v>
       </c>
       <c r="AH39">
-        <v>1E-3</v>
-      </c>
-      <c r="AI39">
-        <v>0.71409999999999996</v>
-      </c>
-      <c r="AJ39">
-        <v>1.1000000000000001E-3</v>
-      </c>
-      <c r="AK39">
-        <v>0.47570000000000001</v>
-      </c>
-      <c r="AL39">
-        <v>2.3E-3</v>
+        <v>0.01</v>
+      </c>
+      <c r="AI39" s="5">
+        <f>AM39*AE39*AG39</f>
+        <v>0.78044400000000003</v>
+      </c>
+      <c r="AJ39" s="5">
+        <f>AI39*SQRT((AF39/AE39)^2+(AH39/AG39)^2+(AN39/AM39)^2)</f>
+        <v>9.8276985856403151E-3</v>
+      </c>
+      <c r="AK39" t="s">
+        <v>117</v>
+      </c>
+      <c r="AL39" t="s">
+        <v>117</v>
       </c>
       <c r="AM39">
-        <v>0.99809999999999999</v>
+        <v>1</v>
       </c>
       <c r="AN39">
-        <v>1.6999999999999999E-3</v>
-      </c>
-      <c r="AO39">
-        <v>0.90129999999999999</v>
-      </c>
-      <c r="AP39">
-        <v>4.4999999999999997E-3</v>
+        <v>6.9999999999999999E-4</v>
+      </c>
+      <c r="AO39" t="s">
+        <v>117</v>
+      </c>
+      <c r="AP39" t="s">
+        <v>117</v>
       </c>
     </row>
     <row r="40" spans="1:42">
@@ -7363,6 +8824,44 @@
       <c r="AD40" t="s">
         <v>123</v>
       </c>
+      <c r="AE40">
+        <v>0.98799999999999999</v>
+      </c>
+      <c r="AF40">
+        <v>2.9999999999999997E-4</v>
+      </c>
+      <c r="AG40">
+        <v>0.89500000000000002</v>
+      </c>
+      <c r="AH40">
+        <v>3.0000000000000001E-3</v>
+      </c>
+      <c r="AI40" s="5">
+        <f>AM40*AE40*AG40</f>
+        <v>0.88470212999999998</v>
+      </c>
+      <c r="AJ40" s="5">
+        <f>AI40*SQRT((AF40/AE40)^2+(AH40/AG40)^2+(AN40/AM40)^2)</f>
+        <v>2.9894180486979504E-3</v>
+      </c>
+      <c r="AK40" t="s">
+        <v>117</v>
+      </c>
+      <c r="AL40" t="s">
+        <v>117</v>
+      </c>
+      <c r="AM40">
+        <v>1.0004999999999999</v>
+      </c>
+      <c r="AN40">
+        <v>2.9999999999999997E-4</v>
+      </c>
+      <c r="AO40" t="s">
+        <v>117</v>
+      </c>
+      <c r="AP40" t="s">
+        <v>117</v>
+      </c>
     </row>
     <row r="41" spans="1:42">
       <c r="A41" t="s">
@@ -7405,7 +8904,43 @@
         <v>43</v>
       </c>
       <c r="AD41" t="s">
-        <v>124</v>
+        <v>112</v>
+      </c>
+      <c r="AE41">
+        <v>0.97130000000000005</v>
+      </c>
+      <c r="AF41">
+        <v>2.3999999999999998E-3</v>
+      </c>
+      <c r="AG41">
+        <v>0.74519999999999997</v>
+      </c>
+      <c r="AH41">
+        <v>2.0899999999999998E-2</v>
+      </c>
+      <c r="AI41">
+        <v>0.72489999999999999</v>
+      </c>
+      <c r="AJ41">
+        <v>2.2700000000000001E-2</v>
+      </c>
+      <c r="AK41">
+        <v>0.52910000000000001</v>
+      </c>
+      <c r="AL41">
+        <v>3.8699999999999998E-2</v>
+      </c>
+      <c r="AM41">
+        <v>1.0015000000000001</v>
+      </c>
+      <c r="AN41">
+        <v>4.2200000000000001E-2</v>
+      </c>
+      <c r="AO41">
+        <v>0.95279999999999998</v>
+      </c>
+      <c r="AP41">
+        <v>8.7800000000000003E-2</v>
       </c>
     </row>
     <row r="42" spans="1:42">
@@ -7449,43 +8984,43 @@
         <v>43</v>
       </c>
       <c r="AD42" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="AE42">
-        <v>0.97130000000000005</v>
+        <v>0.97570000000000001</v>
       </c>
       <c r="AF42">
+        <v>2.0000000000000001E-4</v>
+      </c>
+      <c r="AG42">
+        <v>0.7742</v>
+      </c>
+      <c r="AH42">
+        <v>2.2000000000000001E-3</v>
+      </c>
+      <c r="AI42">
+        <v>0.75800000000000001</v>
+      </c>
+      <c r="AJ42">
         <v>2.3999999999999998E-3</v>
       </c>
-      <c r="AG42">
-        <v>0.74519999999999997</v>
-      </c>
-      <c r="AH42">
-        <v>2.0899999999999998E-2</v>
-      </c>
-      <c r="AI42">
-        <v>0.72489999999999999</v>
-      </c>
-      <c r="AJ42">
-        <v>2.2700000000000001E-2</v>
-      </c>
       <c r="AK42">
-        <v>0.52910000000000001</v>
+        <v>0.58409999999999995</v>
       </c>
       <c r="AL42">
-        <v>3.8699999999999998E-2</v>
+        <v>4.3E-3</v>
       </c>
       <c r="AM42">
-        <v>1.0015000000000001</v>
+        <v>1.0035000000000001</v>
       </c>
       <c r="AN42">
-        <v>4.2200000000000001E-2</v>
+        <v>4.3E-3</v>
       </c>
       <c r="AO42">
-        <v>0.95279999999999998</v>
+        <v>0.97450000000000003</v>
       </c>
       <c r="AP42">
-        <v>8.7800000000000003E-2</v>
+        <v>9.1000000000000004E-3</v>
       </c>
     </row>
     <row r="43" spans="1:42">
@@ -7529,43 +9064,49 @@
         <v>43</v>
       </c>
       <c r="AD43" t="s">
-        <v>113</v>
-      </c>
-      <c r="AE43">
-        <v>0.97570000000000001</v>
-      </c>
-      <c r="AF43">
-        <v>2.0000000000000001E-4</v>
-      </c>
-      <c r="AG43">
-        <v>0.7742</v>
-      </c>
-      <c r="AH43">
-        <v>2.2000000000000001E-3</v>
-      </c>
-      <c r="AI43">
-        <v>0.75800000000000001</v>
-      </c>
-      <c r="AJ43">
-        <v>2.3999999999999998E-3</v>
-      </c>
-      <c r="AK43">
-        <v>0.58409999999999995</v>
-      </c>
-      <c r="AL43">
-        <v>4.3E-3</v>
-      </c>
-      <c r="AM43">
-        <v>1.0035000000000001</v>
-      </c>
-      <c r="AN43">
-        <v>4.3E-3</v>
-      </c>
-      <c r="AO43">
-        <v>0.97450000000000003</v>
-      </c>
-      <c r="AP43">
-        <v>9.1000000000000004E-3</v>
+        <v>106</v>
+      </c>
+      <c r="AE43" s="5">
+        <f>1/1.0063</f>
+        <v>0.99373944151843385</v>
+      </c>
+      <c r="AF43" s="7" t="s">
+        <v>120</v>
+      </c>
+      <c r="AG43" s="5">
+        <f>1/1.32</f>
+        <v>0.75757575757575757</v>
+      </c>
+      <c r="AH43" s="7" t="s">
+        <v>120</v>
+      </c>
+      <c r="AI43" s="5">
+        <f>1/1.33</f>
+        <v>0.75187969924812026</v>
+      </c>
+      <c r="AJ43" s="7" t="s">
+        <v>120</v>
+      </c>
+      <c r="AK43" s="5">
+        <f>1/1.92</f>
+        <v>0.52083333333333337</v>
+      </c>
+      <c r="AL43" s="7" t="s">
+        <v>120</v>
+      </c>
+      <c r="AM43" s="5">
+        <f>AI43/AE43/AG43</f>
+        <v>0.99873383458646614</v>
+      </c>
+      <c r="AN43" s="7" t="s">
+        <v>120</v>
+      </c>
+      <c r="AO43" s="5">
+        <f>AK43/AG43/AG43</f>
+        <v>0.90749999999999997</v>
+      </c>
+      <c r="AP43" s="1" t="s">
+        <v>120</v>
       </c>
     </row>
     <row r="44" spans="1:42">
@@ -7609,7 +9150,49 @@
         <v>43</v>
       </c>
       <c r="AD44" t="s">
-        <v>106</v>
+        <v>107</v>
+      </c>
+      <c r="AE44" s="5">
+        <f>1/1.028</f>
+        <v>0.97276264591439687</v>
+      </c>
+      <c r="AF44" s="7" t="s">
+        <v>120</v>
+      </c>
+      <c r="AG44" s="5">
+        <f>1/1.41</f>
+        <v>0.70921985815602839</v>
+      </c>
+      <c r="AH44" s="7" t="s">
+        <v>120</v>
+      </c>
+      <c r="AI44" s="5">
+        <f>1/1.46</f>
+        <v>0.68493150684931503</v>
+      </c>
+      <c r="AJ44" s="7" t="s">
+        <v>120</v>
+      </c>
+      <c r="AK44" s="5">
+        <f>1/2.2</f>
+        <v>0.45454545454545453</v>
+      </c>
+      <c r="AL44" s="7" t="s">
+        <v>120</v>
+      </c>
+      <c r="AM44" s="5">
+        <f>AI44/AE44/AG44</f>
+        <v>0.99279452054794515</v>
+      </c>
+      <c r="AN44" s="7" t="s">
+        <v>120</v>
+      </c>
+      <c r="AO44" s="5">
+        <f>AK44/AG44/AG44</f>
+        <v>0.90368181818181814</v>
+      </c>
+      <c r="AP44" s="1" t="s">
+        <v>120</v>
       </c>
     </row>
     <row r="45" spans="1:42">
@@ -7652,8 +9235,8 @@
       <c r="Q45" t="s">
         <v>43</v>
       </c>
-      <c r="AD45" t="s">
-        <v>107</v>
+      <c r="AD45" s="6" t="s">
+        <v>118</v>
       </c>
     </row>
     <row r="46" spans="1:42">
@@ -7696,46 +9279,46 @@
       <c r="Q46" t="s">
         <v>43</v>
       </c>
-      <c r="AD46" s="6" t="s">
+      <c r="AD46" t="s">
         <v>119</v>
       </c>
       <c r="AE46">
         <v>0.997</v>
       </c>
       <c r="AF46" s="1" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="AG46">
         <v>0.73399999999999999</v>
       </c>
       <c r="AH46" s="1" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="AI46">
         <v>0.73199999999999998</v>
       </c>
       <c r="AJ46" s="1" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="AK46">
         <v>0.53900000000000003</v>
       </c>
       <c r="AL46" s="1" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="AM46" s="5">
         <f>AI46/AE46/AG46</f>
         <v>1.0002760324570441</v>
       </c>
       <c r="AN46" s="1" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="AO46" s="5">
         <f>AK46/AG46^2</f>
         <v>1.0004528951881744</v>
       </c>
       <c r="AP46" s="1" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="47" spans="1:42">
@@ -7777,9 +9360,6 @@
       </c>
       <c r="Q47" t="s">
         <v>43</v>
-      </c>
-      <c r="AD47" t="s">
-        <v>120</v>
       </c>
     </row>
     <row r="49" spans="1:17">

--- a/fractionation.xlsx
+++ b/fractionation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/f005cbk/Documents/lab/NC10_Radboud/code/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{47BB5777-90C3-C544-8F8A-5155F0A2DB4F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{06F770B2-BB62-FB45-A3D9-009C613A97D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16440" xr2:uid="{2C52F002-3CBE-A64B-89A4-09B4655299CB}"/>
   </bookViews>

--- a/fractionation.xlsx
+++ b/fractionation.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10830"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11207"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/f005cbk/Documents/lab/NC10_Radboud/code/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{06F770B2-BB62-FB45-A3D9-009C613A97D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{14A7AD7E-AF56-104F-9207-7E9F91DD0C5C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16440" xr2:uid="{2C52F002-3CBE-A64B-89A4-09B4655299CB}"/>
   </bookViews>
@@ -415,7 +415,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="172" formatCode="0.0000"/>
+    <numFmt numFmtId="164" formatCode="0.0000"/>
   </numFmts>
   <fonts count="21">
     <font>
@@ -922,11 +922,11 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
     <xf numFmtId="0" fontId="0" fillId="33" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="172" fontId="18" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="172" fontId="19" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="172" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="18" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="19" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="172" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -5712,7 +5712,7 @@
         <v>0.10901421515506791</v>
       </c>
       <c r="AA4">
-        <f t="shared" ref="AA4:AA31" si="7">SQRT((N4/(M4+1000))^2+($N$3/($M$3+1000))^2)</f>
+        <f t="shared" ref="AA4:AA7" si="7">SQRT((N4/(M4+1000))^2+($N$3/($M$3+1000))^2)</f>
         <v>1.1632705690370795E-3</v>
       </c>
     </row>
@@ -5797,7 +5797,7 @@
         <v>8.2550982735605155E-2</v>
       </c>
       <c r="Y5">
-        <f t="shared" ref="Y5:Y31" si="9">SQRT((L5/(K5+1000))^2+($L$3/($K$3+1000))^2)</f>
+        <f t="shared" ref="Y5:Y7" si="9">SQRT((L5/(K5+1000))^2+($L$3/($K$3+1000))^2)</f>
         <v>2.0022313939966076E-4</v>
       </c>
       <c r="Z5">
@@ -8220,19 +8220,19 @@
         <v>1.319E-2</v>
       </c>
       <c r="AM31" s="4">
-        <f t="shared" ref="AM29:AM31" si="46">AI31/AG31/AE31</f>
+        <f t="shared" ref="AM31" si="46">AI31/AG31/AE31</f>
         <v>1.0019523926694696</v>
       </c>
       <c r="AN31" s="4">
-        <f t="shared" ref="AN29:AN31" si="47">AM31*SQRT((AJ31/AI31)^2+(AH31/AG31)^2+(AF31/AE31)^2)</f>
+        <f t="shared" ref="AN31" si="47">AM31*SQRT((AJ31/AI31)^2+(AH31/AG31)^2+(AF31/AE31)^2)</f>
         <v>1.146395968760695E-2</v>
       </c>
       <c r="AO31" s="4">
-        <f t="shared" ref="AO29:AO31" si="48">AK31/AG31^2</f>
+        <f t="shared" ref="AO31" si="48">AK31/AG31^2</f>
         <v>1.0087041348012287</v>
       </c>
       <c r="AP31" s="4">
-        <f t="shared" ref="AP29:AP31" si="49">AO31*SQRT((AL31/AK31)^2+4*(AH31/AG31)^2)</f>
+        <f t="shared" ref="AP31" si="49">AO31*SQRT((AL31/AK31)^2+4*(AH31/AG31)^2)</f>
         <v>2.2097943683816186E-2</v>
       </c>
     </row>
@@ -9362,7 +9362,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="49" spans="1:17">
+    <row r="49" spans="1:22">
       <c r="A49" t="s">
         <v>58</v>
       </c>
@@ -9399,8 +9399,20 @@
       <c r="Q49" t="s">
         <v>60</v>
       </c>
+      <c r="R49">
+        <f t="shared" ref="R49:R58" si="50">-LN(O49)</f>
+        <v>0</v>
+      </c>
+      <c r="T49">
+        <f>LN((C49+1000)/($C$49+1000))</f>
+        <v>0</v>
+      </c>
+      <c r="V49">
+        <f>LN((E49+1000)/($E$49+1000))</f>
+        <v>0</v>
+      </c>
     </row>
-    <row r="50" spans="1:17">
+    <row r="50" spans="1:22">
       <c r="A50" t="s">
         <v>58</v>
       </c>
@@ -9437,8 +9449,20 @@
       <c r="Q50" t="s">
         <v>60</v>
       </c>
+      <c r="R50">
+        <f t="shared" si="50"/>
+        <v>0.43680098841801729</v>
+      </c>
+      <c r="T50">
+        <f t="shared" ref="T50:T58" si="51">LN((C50+1000)/($C$49+1000))</f>
+        <v>1.5780914394237736E-3</v>
+      </c>
+      <c r="V50">
+        <f t="shared" ref="V50:V58" si="52">LN((E50+1000)/($E$49+1000))</f>
+        <v>6.5358868155498309E-2</v>
+      </c>
     </row>
-    <row r="51" spans="1:17">
+    <row r="51" spans="1:22">
       <c r="A51" t="s">
         <v>58</v>
       </c>
@@ -9475,8 +9499,20 @@
       <c r="Q51" t="s">
         <v>60</v>
       </c>
+      <c r="R51">
+        <f t="shared" si="50"/>
+        <v>0.74570443129862141</v>
+      </c>
+      <c r="T51">
+        <f t="shared" si="51"/>
+        <v>3.8277528925790959E-3</v>
+      </c>
+      <c r="V51">
+        <f t="shared" si="52"/>
+        <v>0.11282455664643801</v>
+      </c>
     </row>
-    <row r="52" spans="1:17">
+    <row r="52" spans="1:22">
       <c r="A52" t="s">
         <v>58</v>
       </c>
@@ -9513,8 +9549,20 @@
       <c r="Q52" t="s">
         <v>60</v>
       </c>
+      <c r="R52">
+        <f t="shared" si="50"/>
+        <v>0</v>
+      </c>
+      <c r="T52">
+        <f>LN((C52+1000)/($C$49+1000))</f>
+        <v>0</v>
+      </c>
+      <c r="V52">
+        <f t="shared" si="52"/>
+        <v>0</v>
+      </c>
     </row>
-    <row r="53" spans="1:17">
+    <row r="53" spans="1:22">
       <c r="A53" t="s">
         <v>58</v>
       </c>
@@ -9551,8 +9599,20 @@
       <c r="Q53" t="s">
         <v>60</v>
       </c>
+      <c r="R53">
+        <f t="shared" si="50"/>
+        <v>0.54991301247403757</v>
+      </c>
+      <c r="T53">
+        <f t="shared" si="51"/>
+        <v>1.9151893820141342E-3</v>
+      </c>
+      <c r="V53">
+        <f t="shared" si="52"/>
+        <v>8.2354321430128885E-2</v>
+      </c>
     </row>
-    <row r="54" spans="1:17">
+    <row r="54" spans="1:22">
       <c r="A54" t="s">
         <v>58</v>
       </c>
@@ -9589,8 +9649,20 @@
       <c r="Q54" t="s">
         <v>60</v>
       </c>
+      <c r="R54">
+        <f t="shared" si="50"/>
+        <v>0.88721748438844794</v>
+      </c>
+      <c r="T54">
+        <f t="shared" si="51"/>
+        <v>4.0513026146940124E-3</v>
+      </c>
+      <c r="V54">
+        <f t="shared" si="52"/>
+        <v>0.13082940746714369</v>
+      </c>
     </row>
-    <row r="55" spans="1:17">
+    <row r="55" spans="1:22">
       <c r="A55" t="s">
         <v>58</v>
       </c>
@@ -9627,8 +9699,18 @@
       <c r="Q55" t="s">
         <v>60</v>
       </c>
+      <c r="R55">
+        <f t="shared" si="50"/>
+        <v>0</v>
+      </c>
+      <c r="T55">
+        <v>0</v>
+      </c>
+      <c r="V55">
+        <v>0</v>
+      </c>
     </row>
-    <row r="56" spans="1:17">
+    <row r="56" spans="1:22">
       <c r="A56" t="s">
         <v>58</v>
       </c>
@@ -9665,8 +9747,20 @@
       <c r="Q56" t="s">
         <v>60</v>
       </c>
+      <c r="R56">
+        <f t="shared" si="50"/>
+        <v>0.78789751710575606</v>
+      </c>
+      <c r="T56">
+        <f t="shared" si="51"/>
+        <v>3.9043449992824638E-3</v>
+      </c>
+      <c r="V56">
+        <f t="shared" si="52"/>
+        <v>0.12347802701619767</v>
+      </c>
     </row>
-    <row r="57" spans="1:17">
+    <row r="57" spans="1:22">
       <c r="A57" t="s">
         <v>58</v>
       </c>
@@ -9703,8 +9797,20 @@
       <c r="Q57" t="s">
         <v>60</v>
       </c>
+      <c r="R57">
+        <f t="shared" si="50"/>
+        <v>1.0581423561143963</v>
+      </c>
+      <c r="T57">
+        <f t="shared" si="51"/>
+        <v>6.2840555331212002E-3</v>
+      </c>
+      <c r="V57">
+        <f t="shared" si="52"/>
+        <v>0.16724413538695423</v>
+      </c>
     </row>
-    <row r="58" spans="1:17">
+    <row r="58" spans="1:22">
       <c r="A58" t="s">
         <v>58</v>
       </c>
@@ -9741,8 +9847,20 @@
       <c r="Q58" t="s">
         <v>60</v>
       </c>
+      <c r="R58">
+        <f t="shared" si="50"/>
+        <v>1.3459204669816174</v>
+      </c>
+      <c r="T58">
+        <f t="shared" si="51"/>
+        <v>9.6547375296839738E-3</v>
+      </c>
+      <c r="V58">
+        <f t="shared" si="52"/>
+        <v>0.20610213369617</v>
+      </c>
     </row>
-    <row r="60" spans="1:17">
+    <row r="60" spans="1:22">
       <c r="A60" t="s">
         <v>70</v>
       </c>
@@ -9777,7 +9895,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="61" spans="1:17">
+    <row r="61" spans="1:22">
       <c r="A61" t="s">
         <v>70</v>
       </c>
@@ -9812,7 +9930,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="62" spans="1:17">
+    <row r="62" spans="1:22">
       <c r="A62" t="s">
         <v>70</v>
       </c>
@@ -9847,7 +9965,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="63" spans="1:17">
+    <row r="63" spans="1:22">
       <c r="A63" t="s">
         <v>70</v>
       </c>
@@ -9882,7 +10000,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="64" spans="1:17">
+    <row r="64" spans="1:22">
       <c r="A64" t="s">
         <v>70</v>
       </c>
